--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3583"/>
+  <dimension ref="A1:E3584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97157,6 +97157,33 @@
         </is>
       </c>
     </row>
+    <row r="3584">
+      <c r="A3584" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B3584" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3584" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D3584" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E3584" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3584"/>
+  <dimension ref="A1:E3585"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97184,6 +97184,33 @@
         </is>
       </c>
     </row>
+    <row r="3585">
+      <c r="A3585" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B3585" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3585" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D3585" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E3585" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3585"/>
+  <dimension ref="A1:E3588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97211,6 +97211,87 @@
         </is>
       </c>
     </row>
+    <row r="3586">
+      <c r="A3586" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B3586" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3586" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D3586" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E3586" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
+    <row r="3587">
+      <c r="A3587" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B3587" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3587" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D3587" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E3587" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="3588">
+      <c r="A3588" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B3588" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3588" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D3588" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E3588" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3587"/>
+  <dimension ref="A1:E3588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97265,6 +97265,33 @@
         </is>
       </c>
     </row>
+    <row r="3588">
+      <c r="A3588" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B3588" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3588" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D3588" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E3588" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3588"/>
+  <dimension ref="A1:E3589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97292,6 +97292,33 @@
         </is>
       </c>
     </row>
+    <row r="3589">
+      <c r="A3589" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B3589" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3589" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D3589" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E3589" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3589"/>
+  <dimension ref="A1:E3590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97319,6 +97319,33 @@
         </is>
       </c>
     </row>
+    <row r="3590">
+      <c r="A3590" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B3590" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3590" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D3590" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="E3590" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3590"/>
+  <dimension ref="A1:E3591"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97346,6 +97346,33 @@
         </is>
       </c>
     </row>
+    <row r="3591">
+      <c r="A3591" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B3591" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3591" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D3591" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E3591" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3591"/>
+  <dimension ref="A1:E3592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97373,6 +97373,33 @@
         </is>
       </c>
     </row>
+    <row r="3592">
+      <c r="A3592" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B3592" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3592" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D3592" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E3592" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3592"/>
+  <dimension ref="A1:E3593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97400,6 +97400,33 @@
         </is>
       </c>
     </row>
+    <row r="3593">
+      <c r="A3593" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B3593" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3593" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D3593" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E3593" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3593"/>
+  <dimension ref="A1:E3594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97427,6 +97427,33 @@
         </is>
       </c>
     </row>
+    <row r="3594">
+      <c r="A3594" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B3594" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3594" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D3594" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E3594" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3594"/>
+  <dimension ref="A1:E3595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97454,6 +97454,33 @@
         </is>
       </c>
     </row>
+    <row r="3595">
+      <c r="A3595" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B3595" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3595" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D3595" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E3595" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3595"/>
+  <dimension ref="A1:E3596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97481,6 +97481,33 @@
         </is>
       </c>
     </row>
+    <row r="3596">
+      <c r="A3596" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B3596" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3596" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D3596" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E3596" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3596"/>
+  <dimension ref="A1:E3597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97508,6 +97508,33 @@
         </is>
       </c>
     </row>
+    <row r="3597">
+      <c r="A3597" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B3597" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3597" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D3597" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E3597" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3597"/>
+  <dimension ref="A1:E3598"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97535,6 +97535,33 @@
         </is>
       </c>
     </row>
+    <row r="3598">
+      <c r="A3598" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B3598" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3598" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D3598" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E3598" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3598"/>
+  <dimension ref="A1:E3599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97562,6 +97562,33 @@
         </is>
       </c>
     </row>
+    <row r="3599">
+      <c r="A3599" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B3599" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3599" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D3599" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E3599" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3599"/>
+  <dimension ref="A1:E3600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97589,6 +97589,33 @@
         </is>
       </c>
     </row>
+    <row r="3600">
+      <c r="A3600" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B3600" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3600" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D3600" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E3600" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3600"/>
+  <dimension ref="A1:E3601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97616,6 +97616,33 @@
         </is>
       </c>
     </row>
+    <row r="3601">
+      <c r="A3601" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B3601" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3601" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D3601" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E3601" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3601"/>
+  <dimension ref="A1:E3602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97643,6 +97643,33 @@
         </is>
       </c>
     </row>
+    <row r="3602">
+      <c r="A3602" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B3602" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3602" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D3602" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E3602" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3602"/>
+  <dimension ref="A1:E3603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97670,6 +97670,33 @@
         </is>
       </c>
     </row>
+    <row r="3603">
+      <c r="A3603" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B3603" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3603" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D3603" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E3603" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3603"/>
+  <dimension ref="A1:E3604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97697,6 +97697,33 @@
         </is>
       </c>
     </row>
+    <row r="3604">
+      <c r="A3604" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B3604" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3604" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D3604" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E3604" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3604"/>
+  <dimension ref="A1:E3605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97724,6 +97724,33 @@
         </is>
       </c>
     </row>
+    <row r="3605">
+      <c r="A3605" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B3605" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3605" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="D3605" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E3605" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3605"/>
+  <dimension ref="A1:E3606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97751,6 +97751,33 @@
         </is>
       </c>
     </row>
+    <row r="3606">
+      <c r="A3606" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B3606" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3606" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D3606" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E3606" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3606"/>
+  <dimension ref="A1:E3607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97778,6 +97778,33 @@
         </is>
       </c>
     </row>
+    <row r="3607">
+      <c r="A3607" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B3607" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3607" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="D3607" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E3607" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3607"/>
+  <dimension ref="A1:E3608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97805,6 +97805,33 @@
         </is>
       </c>
     </row>
+    <row r="3608">
+      <c r="A3608" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B3608" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3608" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D3608" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E3608" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3608"/>
+  <dimension ref="A1:E3609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97832,6 +97832,33 @@
         </is>
       </c>
     </row>
+    <row r="3609">
+      <c r="A3609" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B3609" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3609" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D3609" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="E3609" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3609"/>
+  <dimension ref="A1:E3610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97859,6 +97859,33 @@
         </is>
       </c>
     </row>
+    <row r="3610">
+      <c r="A3610" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B3610" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3610" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D3610" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E3610" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
